--- a/kahoot/orientation/finnish-history/main-periods-of-finnish-history-2-independent-finland__0003.xlsx
+++ b/kahoot/orientation/finnish-history/main-periods-of-finnish-history-2-independent-finland__0003.xlsx
@@ -1845,7 +1845,7 @@
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>De flyttade alla till Sverige</t>
+          <t>De flyttade till Sverige</t>
         </is>
       </c>
       <c r="G9" s="14" t="n">
@@ -1892,17 +1892,17 @@
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>De var alla rika</t>
+          <t>Konkurrens om arbete och bostäder</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>De talade bara svenska</t>
+          <t>Rädsla för politiska sympatier</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>De var soldater</t>
+          <t>Oro för ökade kommunala kostnader</t>
         </is>
       </c>
       <c r="G10" s="14" t="n">
@@ -1949,17 +1949,17 @@
       </c>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t>Alla sina språk</t>
+          <t>Sin boskap och sina redskap</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>Alla sina pass</t>
+          <t>Sina identitetshandlingar</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Alla sina skolor</t>
+          <t>Sina arbetsplatser</t>
         </is>
       </c>
       <c r="G11" s="14" t="n">
@@ -2006,17 +2006,17 @@
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>EU-avgift</t>
+          <t>Återuppbyggnadskostnader</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>NATO-avgift</t>
+          <t>Krigslån</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>Tull på kaffe</t>
+          <t>Högre försvarsutgifter</t>
         </is>
       </c>
       <c r="G12" s="14" t="n">
@@ -2120,17 +2120,17 @@
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>Den var klar på en vecka</t>
+          <t>Den gick snabbt tack vare statligt stöd</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Den behövdes inte</t>
+          <t>Den tog några få år</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>Den gjordes av EU direkt</t>
+          <t>Den skedde främst genom privata initiativ</t>
         </is>
       </c>
       <c r="G14" s="14" t="n">
@@ -2234,17 +2234,17 @@
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>De gjorde Finland till en diktatur</t>
+          <t>De ökade misstänksamheten mellan grupper</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>De stoppade all utbildning</t>
+          <t>De skapade politisk instabilitet</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>De tog bort skatter</t>
+          <t>De fördjupade ekonomiska skillnader</t>
         </is>
       </c>
       <c r="G16" s="14" t="n">
@@ -2291,17 +2291,17 @@
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>Finland blev en del av Sovjet</t>
+          <t>Finland förlorade territorium</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>Finland upplöstes</t>
+          <t>Finland betalade krigsskadestånd</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>Finland blev en koloni</t>
+          <t>Finland blev mer beroende av Sovjet</t>
         </is>
       </c>
       <c r="G17" s="14" t="n">
@@ -2348,17 +2348,17 @@
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>Ingen påverkades</t>
+          <t>Många påverkades främst ekonomiskt</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>Alla blev rikare direkt</t>
+          <t>De flesta återhämtade sig snabbt utan långvariga följder</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>Alla flyttade utomlands</t>
+          <t>Hälsoproblem gällde främst de evakuerade</t>
         </is>
       </c>
       <c r="G18" s="14" t="n">
@@ -2405,17 +2405,17 @@
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>För att få euro</t>
+          <t>För att säkra handelsrelationer</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>För att gå med i NATO 1945</t>
+          <t>För att bevara neutraliteten</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>För att avskaffa handel</t>
+          <t>För att undvika politisk konflikt</t>
         </is>
       </c>
       <c r="G19" s="14" t="n">
@@ -2519,17 +2519,17 @@
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>Sluta handla med alla</t>
+          <t>Undvika offentlig kritik mot Sovjet</t>
         </is>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>Avskaffa kommuner</t>
+          <t>Hålla sig militärt neutral</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>Stänga skolor</t>
+          <t>Begränsa samarbetet med väst</t>
         </is>
       </c>
       <c r="G21" s="14" t="n">
@@ -2576,17 +2576,17 @@
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>Den var förbjuden</t>
+          <t>Den var liten och hade liten betydelse</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>Den upphörde helt</t>
+          <t>Den gällde främst jordbruksprodukter</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>Den gällde bara turism</t>
+          <t>Den gällde främst kultur- och studentutbyte</t>
         </is>
       </c>
       <c r="G22" s="14" t="n">
@@ -2633,17 +2633,17 @@
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>All industri stängde</t>
+          <t>Industrin återhämtade sig långsamt</t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>Ekonomin blev helt stillastående</t>
+          <t>Tillväxten var ojämn och periodvis svag</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>All produktion flyttade ut</t>
+          <t>Ekonomin växte långsammare än i Sverige</t>
         </is>
       </c>
       <c r="G23" s="14" t="n">
@@ -2690,17 +2690,17 @@
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>Att avskaffa demokrati</t>
+          <t>Att satsa på industrialisering</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>Att lämna Finland</t>
+          <t>Att bygga fler bostäder</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>Att stoppa skatter helt</t>
+          <t>Att utveckla utbildningssystemet</t>
         </is>
       </c>
       <c r="G24" s="14" t="n">
@@ -2747,17 +2747,17 @@
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>Total isolering</t>
+          <t>Hög sysselsättning</t>
         </is>
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>Noll export</t>
+          <t>Stabila statsfinanser</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr">
         <is>
-          <t>Förbud mot industri</t>
+          <t>Bred skattebas</t>
         </is>
       </c>
       <c r="G25" s="14" t="n">
@@ -2804,17 +2804,17 @@
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>Ingen roll alls</t>
+          <t>Mindre roll än tidigare</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>Bara symbolisk roll</t>
+          <t>Främst ansvar för försvar</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>Enbart militär roll</t>
+          <t>Främst ansvar för infrastruktur</t>
         </is>
       </c>
       <c r="G26" s="14" t="n">
@@ -2861,17 +2861,17 @@
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>Stopp för val</t>
+          <t>Politisk stabilitet</t>
         </is>
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>Förbud mot medier</t>
+          <t>Ekonomisk tillväxt</t>
         </is>
       </c>
       <c r="F27" s="14" t="inlineStr">
         <is>
-          <t>Tvång att flytta</t>
+          <t>Låg korruption</t>
         </is>
       </c>
       <c r="G27" s="14" t="n">
